--- a/technology_surveys/004_impact_of_heat_wave_survey--technology_surveys.xlsx
+++ b/technology_surveys/004_impact_of_heat_wave_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -754,29 +754,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>heat_wave_impacts</t>
+          <t>heat_waves</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Heat Wave Impacts</t>
+          <t>Heat Waves</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>survey_part_1_choices</t>
+          <t>coping_strategies_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>heat_waves</t>
+          <t>air_conditioner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Heat Waves</t>
+          <t>air conditioner</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>air_conditioner</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>air_conditioner</t>
+          <t>fan</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>window_shutter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>window shutter</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>window_shutter</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>window_shutter</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -839,29 +839,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>coping_strategies_choices</t>
+          <t>local_needs_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>air_conditioner</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>air conditioner</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>air_conditioner</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>air_conditioner</t>
+          <t>fan</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>window_shutter</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>window shutter</t>
         </is>
       </c>
     </row>
@@ -907,29 +907,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>window_shutter</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>window_shutter</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>local_needs_choices</t>
+          <t>household_info_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>1_or_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>1 or 2</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1_or_2</t>
+          <t>3_or_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1 or 2</t>
+          <t>3 or 4</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3_or_4</t>
+          <t>5_or_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3 or 4</t>
+          <t>5 or 6</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5_or_6</t>
+          <t>7_or_8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5 or 6</t>
+          <t>7 or 8</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7_or_8</t>
+          <t>9_or_10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7 or 8</t>
+          <t>9 or 10</t>
         </is>
       </c>
     </row>
@@ -1009,29 +1009,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9_or_10</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9 or 10</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>household_info_choices</t>
+          <t>survey_part_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>heat_wave_impacts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Heat Wave Impacts</t>
         </is>
       </c>
     </row>
@@ -1043,46 +1043,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>heat_wave_impacts</t>
+          <t>heat_waves</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Heat Wave Impacts</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>survey_part_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>heat_waves</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>Heat Waves</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>survey_part_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>heat_wave_impacts</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Heat Wave Impacts</t>
         </is>
       </c>
     </row>
